--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="49">
   <si>
     <t>Code*</t>
   </si>
@@ -109,6 +109,63 @@
   </si>
   <si>
     <t>2025-10-28</t>
+  </si>
+  <si>
+    <t>2025-10-31</t>
+  </si>
+  <si>
+    <t>2025-11-03</t>
+  </si>
+  <si>
+    <t>2025-11-04</t>
+  </si>
+  <si>
+    <t>2025-11-10</t>
+  </si>
+  <si>
+    <t>2025-11-11</t>
+  </si>
+  <si>
+    <t>2025-11-12</t>
+  </si>
+  <si>
+    <t>2025-11-14</t>
+  </si>
+  <si>
+    <t>2025-11-18</t>
+  </si>
+  <si>
+    <t>2025-11-19</t>
+  </si>
+  <si>
+    <t>2025-11-20</t>
+  </si>
+  <si>
+    <t>2025-11-24</t>
+  </si>
+  <si>
+    <t>2025-11-25</t>
+  </si>
+  <si>
+    <t>2025-11-26</t>
+  </si>
+  <si>
+    <t>2025-11-28</t>
+  </si>
+  <si>
+    <t>2025-12-01</t>
+  </si>
+  <si>
+    <t>2025-12-05</t>
+  </si>
+  <si>
+    <t>2025-12-10</t>
+  </si>
+  <si>
+    <t>2025-12-12</t>
+  </si>
+  <si>
+    <t>2025-12-15</t>
   </si>
 </sst>
 </file>
@@ -515,19 +572,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>9871.0</v>
+        <v>1504.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>4349.0</v>
+        <v>3203.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>9845.0</v>
+        <v>4263.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>7961.0</v>
+        <v>3169.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -565,19 +622,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1284.0</v>
+        <v>1118.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>6438.0</v>
+        <v>4333.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2094.0</v>
+        <v>2620.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>1982.0</v>
+        <v>4852.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -615,19 +672,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>9168.0</v>
+        <v>1583.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7586.0</v>
+        <v>7161.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>8220.0</v>
+        <v>4255.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>8863.0</v>
+        <v>6757.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="51">
   <si>
     <t>Code*</t>
   </si>
@@ -166,6 +166,12 @@
   </si>
   <si>
     <t>2025-12-15</t>
+  </si>
+  <si>
+    <t>2025-12-16</t>
+  </si>
+  <si>
+    <t>2025-12-17</t>
   </si>
 </sst>
 </file>
@@ -572,19 +578,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1504.0</v>
+        <v>6082.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>3203.0</v>
+        <v>5205.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>4263.0</v>
+        <v>7676.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>3169.0</v>
+        <v>9820.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -622,19 +628,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1118.0</v>
+        <v>8416.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>4333.0</v>
+        <v>3359.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>2620.0</v>
+        <v>3478.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>4852.0</v>
+        <v>5523.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -672,19 +678,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1583.0</v>
+        <v>6024.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7161.0</v>
+        <v>3993.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>4255.0</v>
+        <v>3184.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>6757.0</v>
+        <v>7701.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="52">
   <si>
     <t>Code*</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>2025-12-17</t>
+  </si>
+  <si>
+    <t>2025-12-19</t>
   </si>
 </sst>
 </file>
@@ -578,19 +581,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>6082.0</v>
+        <v>6470.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>5205.0</v>
+        <v>2595.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>7676.0</v>
+        <v>5944.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>9820.0</v>
+        <v>8734.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -628,19 +631,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>8416.0</v>
+        <v>2066.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>3359.0</v>
+        <v>4906.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3478.0</v>
+        <v>8413.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>5523.0</v>
+        <v>6556.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -678,19 +681,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>6024.0</v>
+        <v>7048.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>3993.0</v>
+        <v>7225.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>3184.0</v>
+        <v>6949.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>7701.0</v>
+        <v>7450.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="53">
   <si>
     <t>Code*</t>
   </si>
@@ -175,6 +175,9 @@
   </si>
   <si>
     <t>2025-12-19</t>
+  </si>
+  <si>
+    <t>2026-01-29</t>
   </si>
 </sst>
 </file>
@@ -581,19 +584,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>6470.0</v>
+        <v>8751.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>2595.0</v>
+        <v>1402.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>5944.0</v>
+        <v>9607.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>8734.0</v>
+        <v>4974.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -631,19 +634,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>2066.0</v>
+        <v>5238.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>4906.0</v>
+        <v>3807.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>8413.0</v>
+        <v>8209.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>6556.0</v>
+        <v>3460.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -681,19 +684,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>7048.0</v>
+        <v>6086.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>7225.0</v>
+        <v>6035.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>6949.0</v>
+        <v>2983.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>7450.0</v>
+        <v>9195.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="58">
   <si>
     <t>Code*</t>
   </si>
@@ -178,6 +178,21 @@
   </si>
   <si>
     <t>2026-01-29</t>
+  </si>
+  <si>
+    <t>2026-04-13</t>
+  </si>
+  <si>
+    <t>2026-04-27</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-06</t>
+  </si>
+  <si>
+    <t>2026-05-07</t>
   </si>
 </sst>
 </file>
@@ -584,19 +599,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>8751.0</v>
+        <v>1528.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1402.0</v>
+        <v>8709.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>9607.0</v>
+        <v>2730.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>4974.0</v>
+        <v>7954.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -634,19 +649,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>5238.0</v>
+        <v>1875.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>3807.0</v>
+        <v>7548.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>8209.0</v>
+        <v>3856.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>3460.0</v>
+        <v>7991.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -684,19 +699,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>6086.0</v>
+        <v>1848.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>6035.0</v>
+        <v>1753.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>2983.0</v>
+        <v>6914.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>9195.0</v>
+        <v>3922.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="60">
   <si>
     <t>Code*</t>
   </si>
@@ -193,6 +193,12 @@
   </si>
   <si>
     <t>2026-05-07</t>
+  </si>
+  <si>
+    <t>2026-05-08</t>
+  </si>
+  <si>
+    <t>2026-05-11</t>
   </si>
 </sst>
 </file>
@@ -599,19 +605,19 @@
         <v>22</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1528.0</v>
+        <v>8105.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>8709.0</v>
+        <v>7149.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>2730.0</v>
+        <v>2131.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>7954.0</v>
+        <v>1772.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -649,19 +655,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1875.0</v>
+        <v>9114.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>7548.0</v>
+        <v>1594.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>3856.0</v>
+        <v>7464.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>7991.0</v>
+        <v>9206.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -699,19 +705,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>1848.0</v>
+        <v>3698.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>1753.0</v>
+        <v>2847.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>6914.0</v>
+        <v>5899.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>3922.0</v>
+        <v>4798.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>

--- a/ResourcesPK/productPrice.xlsx
+++ b/ResourcesPK/productPrice.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="203">
   <si>
     <t>Code*</t>
   </si>
@@ -102,103 +102,532 @@
     <t>LUX ALLURE TRIO WHITE PI4 36X3X130G</t>
   </si>
   <si>
-    <t>2025-10-09</t>
-  </si>
-  <si>
-    <t>2025-10-27</t>
-  </si>
-  <si>
-    <t>2025-10-28</t>
-  </si>
-  <si>
-    <t>2025-10-31</t>
-  </si>
-  <si>
-    <t>2025-11-03</t>
-  </si>
-  <si>
-    <t>2025-11-04</t>
-  </si>
-  <si>
-    <t>2025-11-10</t>
-  </si>
-  <si>
-    <t>2025-11-11</t>
-  </si>
-  <si>
-    <t>2025-11-12</t>
-  </si>
-  <si>
-    <t>2025-11-14</t>
-  </si>
-  <si>
-    <t>2025-11-18</t>
-  </si>
-  <si>
-    <t>2025-11-19</t>
-  </si>
-  <si>
-    <t>2025-11-20</t>
-  </si>
-  <si>
-    <t>2025-11-24</t>
-  </si>
-  <si>
-    <t>2025-11-25</t>
-  </si>
-  <si>
-    <t>2025-11-26</t>
-  </si>
-  <si>
-    <t>2025-11-28</t>
-  </si>
-  <si>
-    <t>2025-12-01</t>
-  </si>
-  <si>
-    <t>2025-12-05</t>
-  </si>
-  <si>
-    <t>2025-12-10</t>
-  </si>
-  <si>
-    <t>2025-12-12</t>
-  </si>
-  <si>
-    <t>2025-12-15</t>
-  </si>
-  <si>
-    <t>2025-12-16</t>
-  </si>
-  <si>
-    <t>2025-12-17</t>
-  </si>
-  <si>
-    <t>2025-12-19</t>
-  </si>
-  <si>
-    <t>2026-01-29</t>
-  </si>
-  <si>
-    <t>2026-04-13</t>
-  </si>
-  <si>
-    <t>2026-04-27</t>
-  </si>
-  <si>
-    <t>2026-04-30</t>
-  </si>
-  <si>
-    <t>2026-05-06</t>
-  </si>
-  <si>
-    <t>2026-05-07</t>
-  </si>
-  <si>
-    <t>2026-05-08</t>
-  </si>
-  <si>
     <t>2026-05-11</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>2026-05-20</t>
+  </si>
+  <si>
+    <t>3080.0</t>
+  </si>
+  <si>
+    <t>9627.0</t>
+  </si>
+  <si>
+    <t>1165.0</t>
+  </si>
+  <si>
+    <t>1082.0</t>
+  </si>
+  <si>
+    <t>8736.0</t>
+  </si>
+  <si>
+    <t>4759.0</t>
+  </si>
+  <si>
+    <t>3831.0</t>
+  </si>
+  <si>
+    <t>9044.0</t>
+  </si>
+  <si>
+    <t>4413.0</t>
+  </si>
+  <si>
+    <t>8938.0</t>
+  </si>
+  <si>
+    <t>7325.0</t>
+  </si>
+  <si>
+    <t>7525.0</t>
+  </si>
+  <si>
+    <t>6022.0</t>
+  </si>
+  <si>
+    <t>7251.0</t>
+  </si>
+  <si>
+    <t>5401.0</t>
+  </si>
+  <si>
+    <t>4490.0</t>
+  </si>
+  <si>
+    <t>7659.0</t>
+  </si>
+  <si>
+    <t>6369.0</t>
+  </si>
+  <si>
+    <t>5239.0</t>
+  </si>
+  <si>
+    <t>5687.0</t>
+  </si>
+  <si>
+    <t>5553.0</t>
+  </si>
+  <si>
+    <t>5032.0</t>
+  </si>
+  <si>
+    <t>8266.0</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>1984.0</t>
+  </si>
+  <si>
+    <t>6889.0</t>
+  </si>
+  <si>
+    <t>2930.0</t>
+  </si>
+  <si>
+    <t>8694.0</t>
+  </si>
+  <si>
+    <t>5735.0</t>
+  </si>
+  <si>
+    <t>3298.0</t>
+  </si>
+  <si>
+    <t>4454.0</t>
+  </si>
+  <si>
+    <t>6764.0</t>
+  </si>
+  <si>
+    <t>3068.0</t>
+  </si>
+  <si>
+    <t>2966.0</t>
+  </si>
+  <si>
+    <t>5198.0</t>
+  </si>
+  <si>
+    <t>9430.0</t>
+  </si>
+  <si>
+    <t>2255.0</t>
+  </si>
+  <si>
+    <t>4415.0</t>
+  </si>
+  <si>
+    <t>2094.0</t>
+  </si>
+  <si>
+    <t>1364.0</t>
+  </si>
+  <si>
+    <t>1187.0</t>
+  </si>
+  <si>
+    <t>9653.0</t>
+  </si>
+  <si>
+    <t>6063.0</t>
+  </si>
+  <si>
+    <t>5184.0</t>
+  </si>
+  <si>
+    <t>5939.0</t>
+  </si>
+  <si>
+    <t>3393.0</t>
+  </si>
+  <si>
+    <t>4070.0</t>
+  </si>
+  <si>
+    <t>2193.0</t>
+  </si>
+  <si>
+    <t>7938.0</t>
+  </si>
+  <si>
+    <t>6098.0</t>
+  </si>
+  <si>
+    <t>2360.0</t>
+  </si>
+  <si>
+    <t>9038.0</t>
+  </si>
+  <si>
+    <t>3321.0</t>
+  </si>
+  <si>
+    <t>5834.0</t>
+  </si>
+  <si>
+    <t>3398.0</t>
+  </si>
+  <si>
+    <t>5977.0</t>
+  </si>
+  <si>
+    <t>3514.0</t>
+  </si>
+  <si>
+    <t>8104.0</t>
+  </si>
+  <si>
+    <t>4733.0</t>
+  </si>
+  <si>
+    <t>7153.0</t>
+  </si>
+  <si>
+    <t>7367.0</t>
+  </si>
+  <si>
+    <t>9358.0</t>
+  </si>
+  <si>
+    <t>5544.0</t>
+  </si>
+  <si>
+    <t>2512.0</t>
+  </si>
+  <si>
+    <t>1832.0</t>
+  </si>
+  <si>
+    <t>1207.0</t>
+  </si>
+  <si>
+    <t>9879.0</t>
+  </si>
+  <si>
+    <t>2587.0</t>
+  </si>
+  <si>
+    <t>4517.0</t>
+  </si>
+  <si>
+    <t>5837.0</t>
+  </si>
+  <si>
+    <t>8580.0</t>
+  </si>
+  <si>
+    <t>8037.0</t>
+  </si>
+  <si>
+    <t>2262.0</t>
+  </si>
+  <si>
+    <t>9776.0</t>
+  </si>
+  <si>
+    <t>3858.0</t>
+  </si>
+  <si>
+    <t>4109.0</t>
+  </si>
+  <si>
+    <t>8955.0</t>
+  </si>
+  <si>
+    <t>1499.0</t>
+  </si>
+  <si>
+    <t>5505.0</t>
+  </si>
+  <si>
+    <t>4015.0</t>
+  </si>
+  <si>
+    <t>3521.0</t>
+  </si>
+  <si>
+    <t>8178.0</t>
+  </si>
+  <si>
+    <t>3912.0</t>
+  </si>
+  <si>
+    <t>1528.0</t>
+  </si>
+  <si>
+    <t>7914.0</t>
+  </si>
+  <si>
+    <t>9806.0</t>
+  </si>
+  <si>
+    <t>3540.0</t>
+  </si>
+  <si>
+    <t>4048.0</t>
+  </si>
+  <si>
+    <t>6242.0</t>
+  </si>
+  <si>
+    <t>2410.0</t>
+  </si>
+  <si>
+    <t>7568.0</t>
+  </si>
+  <si>
+    <t>2168.0</t>
+  </si>
+  <si>
+    <t>5261.0</t>
+  </si>
+  <si>
+    <t>2366.0</t>
+  </si>
+  <si>
+    <t>4849.0</t>
+  </si>
+  <si>
+    <t>2471.0</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>1021.0</t>
+  </si>
+  <si>
+    <t>1656.0</t>
+  </si>
+  <si>
+    <t>2264.0</t>
+  </si>
+  <si>
+    <t>2892.0</t>
+  </si>
+  <si>
+    <t>2741.0</t>
+  </si>
+  <si>
+    <t>3527.0</t>
+  </si>
+  <si>
+    <t>2828.0</t>
+  </si>
+  <si>
+    <t>5794.0</t>
+  </si>
+  <si>
+    <t>4657.0</t>
+  </si>
+  <si>
+    <t>1109.0</t>
+  </si>
+  <si>
+    <t>5715.0</t>
+  </si>
+  <si>
+    <t>8005.0</t>
+  </si>
+  <si>
+    <t>3616.0</t>
+  </si>
+  <si>
+    <t>4388.0</t>
+  </si>
+  <si>
+    <t>3665.0</t>
+  </si>
+  <si>
+    <t>5919.0</t>
+  </si>
+  <si>
+    <t>4333.0</t>
+  </si>
+  <si>
+    <t>7504.0</t>
+  </si>
+  <si>
+    <t>6279.0</t>
+  </si>
+  <si>
+    <t>7339.0</t>
+  </si>
+  <si>
+    <t>7014.0</t>
+  </si>
+  <si>
+    <t>3940.0</t>
+  </si>
+  <si>
+    <t>3515.0</t>
+  </si>
+  <si>
+    <t>3420.0</t>
+  </si>
+  <si>
+    <t>1579.0</t>
+  </si>
+  <si>
+    <t>7863.0</t>
+  </si>
+  <si>
+    <t>5446.0</t>
+  </si>
+  <si>
+    <t>2974.0</t>
+  </si>
+  <si>
+    <t>2452.0</t>
+  </si>
+  <si>
+    <t>5648.0</t>
+  </si>
+  <si>
+    <t>4978.0</t>
+  </si>
+  <si>
+    <t>2053.0</t>
+  </si>
+  <si>
+    <t>5869.0</t>
+  </si>
+  <si>
+    <t>2466.0</t>
+  </si>
+  <si>
+    <t>9272.0</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>7587.0</t>
+  </si>
+  <si>
+    <t>6663.0</t>
+  </si>
+  <si>
+    <t>4450.0</t>
+  </si>
+  <si>
+    <t>5818.0</t>
+  </si>
+  <si>
+    <t>5230.0</t>
+  </si>
+  <si>
+    <t>3340.0</t>
+  </si>
+  <si>
+    <t>2567.0</t>
+  </si>
+  <si>
+    <t>2714.0</t>
+  </si>
+  <si>
+    <t>1446.0</t>
+  </si>
+  <si>
+    <t>7519.0</t>
+  </si>
+  <si>
+    <t>5700.0</t>
+  </si>
+  <si>
+    <t>9296.0</t>
+  </si>
+  <si>
+    <t>2032.0</t>
+  </si>
+  <si>
+    <t>1236.0</t>
+  </si>
+  <si>
+    <t>5647.0</t>
+  </si>
+  <si>
+    <t>2427.0</t>
+  </si>
+  <si>
+    <t>9839.0</t>
+  </si>
+  <si>
+    <t>2455.0</t>
+  </si>
+  <si>
+    <t>9165.0</t>
+  </si>
+  <si>
+    <t>3725.0</t>
+  </si>
+  <si>
+    <t>7149.0</t>
+  </si>
+  <si>
+    <t>7628.0</t>
+  </si>
+  <si>
+    <t>1095.0</t>
+  </si>
+  <si>
+    <t>6429.0</t>
+  </si>
+  <si>
+    <t>2026-06-29</t>
+  </si>
+  <si>
+    <t>8688.0</t>
+  </si>
+  <si>
+    <t>4276.0</t>
+  </si>
+  <si>
+    <t>8231.0</t>
+  </si>
+  <si>
+    <t>3006.0</t>
+  </si>
+  <si>
+    <t>2329.0</t>
+  </si>
+  <si>
+    <t>6871.0</t>
+  </si>
+  <si>
+    <t>4293.0</t>
+  </si>
+  <si>
+    <t>7044.0</t>
+  </si>
+  <si>
+    <t>8278.0</t>
+  </si>
+  <si>
+    <t>9726.0</t>
+  </si>
+  <si>
+    <t>9628.0</t>
+  </si>
+  <si>
+    <t>6940.0</t>
+  </si>
+  <si>
+    <t>2026-07-02</t>
+  </si>
+  <si>
+    <t>2026-07-07</t>
+  </si>
+  <si>
+    <t>2026-07-08</t>
   </si>
 </sst>
 </file>
@@ -522,11 +951,20 @@
   <dimension ref="A1:P4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="18.6328125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="35.0"/>
-    <col min="4" max="4" customWidth="true" width="13.36328125"/>
-    <col min="9" max="9" customWidth="true" width="14.6328125"/>
-    <col min="10" max="16" style="1" width="8.0"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="8.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="5.81640625"/>
+    <col min="3" max="4" bestFit="true" customWidth="true" width="35.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="18.08984375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="36.81640625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="5.81640625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="5.36328125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.90625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="13.7265625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.08984375"/>
+    <col min="13" max="13" style="1" width="8.0"/>
+    <col min="14" max="15" bestFit="true" customWidth="true" style="1" width="9.90625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="3.54296875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -601,23 +1039,23 @@
       <c r="G2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>22</v>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>8105.0</v>
+        <v>4493.0</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>7149.0</v>
+        <v>9351.0</v>
       </c>
       <c r="L2" s="1" t="n">
-        <v>2131.0</v>
+        <v>7198.0</v>
       </c>
       <c r="M2" s="1" t="n">
-        <v>1772.0</v>
+        <v>7389.0</v>
       </c>
       <c r="N2" s="1">
         <v>7451</v>
@@ -655,19 +1093,19 @@
         <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>9114.0</v>
+        <v>1890.0</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1594.0</v>
+        <v>3990.0</v>
       </c>
       <c r="L3" s="1" t="n">
-        <v>7464.0</v>
+        <v>3292.0</v>
       </c>
       <c r="M3" s="1" t="n">
-        <v>9206.0</v>
+        <v>3009.0</v>
       </c>
       <c r="N3" s="1">
         <v>3094</v>
@@ -705,19 +1143,19 @@
         <v>22</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>59</v>
+        <v>202</v>
       </c>
       <c r="J4" s="1" t="n">
-        <v>3698.0</v>
+        <v>1994.0</v>
       </c>
       <c r="K4" s="1" t="n">
-        <v>2847.0</v>
+        <v>3597.0</v>
       </c>
       <c r="L4" s="1" t="n">
-        <v>5899.0</v>
+        <v>8599.0</v>
       </c>
       <c r="M4" s="1" t="n">
-        <v>4798.0</v>
+        <v>2843.0</v>
       </c>
       <c r="N4" s="1">
         <v>4537</v>
